--- a/mistral-large-latest.xlsx
+++ b/mistral-large-latest.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG19"/>
+  <dimension ref="A1:AG42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3548,6 +3548,3801 @@
         </is>
       </c>
       <c r="AG19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2022-2-DiamondD-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>At about 1500</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>North Shields</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>At 1453, used Diamond D ’s main VHF radio to call Humber coastguard on channel 16 and request assistance</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>The crew was attempting to uncross the towing wires and haul in the trawl gear.</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>Tynemouth all-weather lifeboat (ALB)</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>The crew member retrieved safety equipment from the wheelhouse and other parts of the vessel. Specific items mentioned include the EPIRB from the wheelhouse roof, a handheld VHF radio from inside the wheelhouse, lifejackets, a box of flares, and a small personal bag containing medication and dry clothes.</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Yes, at 1453, the skipper used Diamond D’s main VHF radio to call Humber coastguard on channel 16 and request assistance.</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2, the permanent skipper and owner</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2024-1-EderSands-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>at about 1915</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Ondar Fishing Company Limited</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>North Atlantic</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>Wind westerly at 8kts; 1m seas; dark, with good visibility; estimated sea temperature 14.8°C.</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>shooting fishing gear</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>20 people were onboard at the time of the accident, including a Spanish master, mate, chief engineer and bosun, and 16 Indonesian nationals.</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2024-1-EderSands-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>At about 1915</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ondar Fishing Company Limited</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Yes, the vessel was shooting fishing gear and operating under normal conditions.</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>North Atlantic</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>Wind westerly at 8kts; 1m seas; dark, with good visibility; estimated sea temperature 14.8°C</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>the deckhand at the stern shouted to stop the vessel and call the bosun</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>20 people were onboard. They were a Spanish master, mate, chief engineer and bosun and 16 Indonesian nationals.</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>good visibility</t>
+        </is>
+      </c>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2023-2-HarrietJ-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>28 August 2021 at about 0736</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>The vessel was heading east after shooting the fourth fleet.</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>5.4kts</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>Long 1.2m northerly swell; air temperature 12°C; wind south-westerly force 3; sea temperature approximately 15°C</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>The skipper probably accessed the working deck to free a snag in the fourth fleet of creels as it was being deployed from the vessel.</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>about 0736</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>less than 5m</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>Yes, 43.4%</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>3.5</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG23" t="inlineStr">
+        <is>
+          <t>Harriet J traveled approximately 0.9 nautical miles</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2023-2-HarrietJ-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>at about 0736</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>St Abbs (intended)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>5.4kts</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1997</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Long 1.2m northerly swell; air temperature 12°C; wind south-westerly force 3; sea temperature approximately 15°C</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>The skipper’s normal practice was to remain in the wheelhouse or at the controls at the forward end of the working deck as the weights and creels were being shot.</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>at about 0736</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>1, the skipper</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>less than 5m</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD24" t="inlineStr">
+        <is>
+          <t>Yes, 81% decrease in speed (from 5.4kts to approximately 1kt)</t>
+        </is>
+      </c>
+      <c r="AE24" t="inlineStr">
+        <is>
+          <t>3 hours</t>
+        </is>
+      </c>
+      <c r="AF24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG24" t="inlineStr">
+        <is>
+          <t>Yes, 0.9nm</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2023-1-EmmaLouise-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>In the early evening on 11 January 2022</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>William Traynor</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>2 fatalities</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>It was drizzling with light, occasionally gentle, northerly wind, the air temperature was 10˚C and there was no swell; there were squally rain showers later in the evening.</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>At 1727, the owner called his wife and told her that he and his brother-in-law were sitting in the cockpit with the canopy closed, each drinking a beer.</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>Each drank a beer; the meal and red wine were untouched.</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2; the owner William Tranor and his brother-in-law Martin Steventon</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2023-1-EmmaLouise-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>GTS sports cruise r</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1996</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>5.5m</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>4 cylinder 3.0 litre inboard petrol engine</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Glass reinforced plastic</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Port Hamble Marina, Hampshire</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>11 January 2022 in the early evening</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Not applicable</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>In the early evening</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2, Emma Louise's owner, William Trainer, and his brother-in-law, Martin Steventon</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2022-14-ReulAChuain.pdf</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>At about 1850</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Mallaig</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>6.5kts</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>In transit</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>a force 6 north wind creating a short steep swell that caused Reul A Chuain to roll heavily.</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>trying to recover one of the vessel’s nets, which had slipped over the stern during heavy rolling.</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>Mallaig ALB</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>The junior deckhand retrieved the lifebuoys from the foredeck of Reul A Chuain.</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>The junior deckhand had not taken part in a practical man overboard drill on Reul A Chuain and consequently was unaware of the presence of any man overboard recovery equipment.</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>3 crew</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD27" t="inlineStr">
+        <is>
+          <t>Yes, 53.85% decrease in speed from 6.5kts to neutral</t>
+        </is>
+      </c>
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2022-14-ReulAChuain.pdf</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>At about 1850</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Mr Robertson</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mallaig</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>6.5kts</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1959</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>"The wind had veered to the north and increased to a force 6, creating a short steep swell that caused Reul A Chuain  to roll heavily."</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>"The crew member's activity around the time of the accident was trying to recover one of the vessel’s nets, which had slipped over the stern during heavy rolling."</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>"Mallaig ALB"</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>3; the skipper, the senior deckhand, and the junior deckhand</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>Yes, 53.85% decrease in speed from 6.5kts to 0kts</t>
+        </is>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2022-11-Goodway-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>At about 1340</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Joe Masson</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Cairnbulg Briggs reef</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>One presumed fatality</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>No VHF, DSC or AIS distress alert was received from Goodway</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>Wind force 2 to 3, slight sea, low swell, sea temperature 12°C, visibility good.</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>The owner was fishing alone, near to where his vessel was found, and that it was anchored to a fleet of creels on the seabed.</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>1, the owner</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2022-11-Goodway-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>at about 1340</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Joe Masson</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Cairnbulg Briggs reef</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>One presumed fatality</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>No VHF, DSC or AIS distress alert was received from Goodway.</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>Wind force 2 to 3, slight sea, low swell, sea temperature 12°C, visibility good.</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>The owner was fishing alone, near to where his vessel was found, and that it was anchored to a fleet of creels on the seabed.</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>1440</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>1; the owner</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>visibility good.</t>
+        </is>
+      </c>
+      <c r="AD30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2022-10-Bella-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>at about 1506</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Geosight Limited</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>about 5 knots</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Yes, the crew member made a "Mayday!" call using the hand-held very high frequency (VHF) radio, used a mobile phone to report the emergency to the supervisor ashore and then, at 1506, called 999 to notify the coastguard, and used a flare to attract attention as Bella sank.</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>wind north-westerly force 3; wave height 0.5m-1.0m</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>The crew member went forward and lowered the multibeam echo sounder (MBES) gantry from its stowed position into the sea.</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>rigid inflatable boats (RIB)</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>The crew member used a mobile phone to report the emergency to the supervisor ashore and then, at 1506, called 999 to notify the coastguard.</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>The skipper held a seafarer’s medical certificate and had completed a Royal Yachting Association (RYA) accredited sea survival course. The crew member did not hold a valid seafarers’ medical certificate and had not completed any other marine training.</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>At about 1506</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2 people: the skipper and a crew member</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2022-10-Bella-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Geosight Limited</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>5 knots</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Yes, a "Mayday!" call was sent out using the hand-held very high frequency (VHF) radio, and a mobile phone was used to report the emergency to the supervisor ashore and then to call 999 to notify the coastguard.</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>North Devon, England</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>wind north-westerly force 3; wave height 0.5m-1.0m</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>lowered the multibeam echo sounder (MBES) gantry from its stowed position into the sea</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>rigid inflatable boats (RIB)</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>The skipper told the crew member to make a “Mayday!” call using the hand-held very high frequency (VHF) radio. No response was heard to the VHF “Mayday!” call, so the crew member used a mobile phone to report the emergency to the supervisor ashore and then, at 1506, called 999 to notify the coastguard.</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>The vessel did not have any cargo (None).</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>1506</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2 people were onboard: the skipper and a crew member</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2022-6-SaintPeter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>between 0800 and1000</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Privately owned</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Cove, Scotland (intended)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>shooting creels</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>1, the owner/skipper</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2022-6-SaintPeter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>North Sea</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>shooting creels</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>The wheelhouse throttle control was not operational</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>At about 0830</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>1 person: the owner/skipper (the skipper)</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2021-14-Achieve-Talis-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>8 November 2020 at 1541</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>WeShips Denizcilik ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Terneuzen, Netherlands</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Talis was built in 1992.</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>wind SSE force 2 to 3, slight sea, low swell. Overcast, poor visibility in patchy fog.</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>The C/O contacted the duty able-bodied seaman (AB) in his cabin and told him to come to the bridge to keep a lookout.</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>Tynemouth RNLI all-weather lifeboat (ALB)</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Yes, "At 1544, Achieve’s skipper called Humber Coastguard on very high frequency (VHF) radio channel 16 and advised them he had been in a collision and was taking on water."</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Yes, "Both the skipper and the deckhand had completed all UK statutory safety courses."</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>1600</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>1nm</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>2646</t>
+        </is>
+      </c>
+      <c r="AG35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2021-14-Achieve-Talis-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>At 1541</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>WeShips Denizcilik ve Ticaret A.Ş.</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Terneuzen, Netherlands</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>8.2kts</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>Wind SSE force 2 to 3, slight sea, low swell. Overcast, poor visibility in patchy fog.</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>Tynemouth RNLI all-weather lifeboat (ALB)</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Achieve’s skipper called Humber Coastguard on very high frequency (VHF) radio channel 16 and advised them he had been in a collision and was taking on water.</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Both the skipper and the deckhand had completed all UK statutory safety courses.</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>Two people were onboard at the time of the accident, the skipper and the deckhand.</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>1nm</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>fog patches</t>
+        </is>
+      </c>
+      <c r="AD36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>2646</t>
+        </is>
+      </c>
+      <c r="AG36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2021-10-Globetrotter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>fishing grounds</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>The vessel was operating on a coastal voyage from Fleetwood, England, to Fleetwood, England.</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>0742, Globetrotter ’s owner used the hand-held radio to broadcast a “Mayday” on VHF channel 16.</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>The weather was fine and clear, the wind was easterly Beaufort force 3 to 4.</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>The owner’s son pointed out to his father that there was water on the deck aft.</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>The Fleetwood Royal National Lifeboat Institution (RNLI) inshore lifeboat and Fleetwood’s all-weather lifeboat.</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>The crew member retrieved safety equipment from the forward cabin and the cabin door.</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>The crew was not properly trained for handling emergency situations.</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>3 people were onboard: Globetrotter’s owner, his son, and his friend</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>Pisces was nearby, distance not specified</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2021-10-Globetrotter-Report.pdf</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>a fishing trip</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>One fatality</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>On passage</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>"Mayday"</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>The weather was fine and clear, the wind was easterly Beaufort force 3 to 4, the tide was ebbing in a south-westerly direction at a rate of about 0.6 knot, and the sea water temperature was 15.3°C.</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>The crew member was rigging their fishing lines.</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>Fleetwood Royal National Lifeboat Institution (RNLI) inshore lifeboat and Fleetwood’s all-weather lifeboat.</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>The cabin space and by the cabin door.</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Yes, Globetrotter's owner contacted Fivebuoys' skipper by mobile telephone at 0724 to discuss steering problems and at 0747 to inform him that Globetrotter was sinking. He also broadcast a "Mayday" on VHF channel 16 at 0742, which was received by Holyhead Coastguard.</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>No, Globetrotter's owner and his friend were unaware of the SOLAS regulations, MGN 599 (M) or Emily’s Code and had no formal maritime qualifications and had not completed any safety courses.</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>Three people were onboard: Globetrotter's owner, his son, and his friend.</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2021-06-BeinnNaCaillich.pdf</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>At 1510</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Marine Harvest (Scotland) Limited</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ardintoul Point, Loch Alsh</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Still moving slowly ahead</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>a vertical fender on the right-hand side of the ladder was missing after becoming detached following a heavy contact during a feed delivery on 8 February 2020.</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>At 1520, Stornoway Coastguard received a “Mayday” call from the barge on very high frequency (VHF) radio channel 16, and shortly afterwards a “Mayday” call from Beinn Na Caillich.</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>"the wind was south-westerly at 15 knots, the sea state was slight, the air temperature was 5°C and the water temperature was about 7°C."</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>"The assistant manager was attempting to climb on to the barge from the workboat Beinn Na Caillich and fell into the water after being crushed between the boat and the barge."</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>"RBB"</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>At 1520, Stornoway Coastguard received a “Mayday” call from the barge on very high frequency (VHF) radio channel 16, and shortly afterwards a “Mayday” call from Beinn Na Caillich.</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Emergency drills were rarely conducted on board Beinn Na Caillich and there were no records of them having taken place.</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>1610</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>5 people were onboard: Beinn Na Caillich’s skipper, the deckhand, the assistant manager, and two crewmen from Stolt Madah.</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2021-06-BeinnNaCaillich.pdf</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>1510</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Marine Harvest (Scotland) Limited</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Ardintoul fish farm site</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>still moving slowly ahead</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>The wind was south-westerly at 15 knots, the sea state was slight, the air temperature was 5°C and the water temperature was about 7°C.</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>The assistant manager was attempting to climb onto the barge from the workboat Beinn Na Caillich.</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>RBB (Rigid Buoyancy Boat)</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>At 1520, Stornoway Coastguard received a “Mayday” call from the barge on very high frequency (VHF) radio channel 16, and shortly afterwards a “Mayday” call from Beinn Na Caillich.</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Emergency drills were rarely conducted on board Beinn Na Caillich and there were no records of them having taken place.</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>1610</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>5 people were onboard: Beinn Na Caillich's skipper, a deckhand, the assistant manager, Stolt Madah’s skipper, and a fish farm technician.</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2021-Seadogz_InterimReport.pdf</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>22 August 2020, 1011:09</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Very Serious Marine Casualty</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Southampton Water</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>bow</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>10 injured, 1 fatality</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>West-south-westerly winds, force 4-5, slight seas, overcast with bright spells, good visibility</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>The skipper was concentrating on conducting high speed manoeuvres in close proximity to another vessel.</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>1011:09</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>There were 12 people onboard at the time of the accident. They were 11 passengers and 1 skipper.</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2021-Seadogz_InterimReport.pdf</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>mistral-large-latest</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1011:09</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Seadogz Rib Charter Ltd</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>38.4kts</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>1 fatality</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>West-south-westerly winds, force 4-5, slight seas, overcast with bright spells, good visibility</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>The skipper was concentrating on conducting high speed manoeuvres in close proximity to another vessel</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>The incident occurred at 1011:09 on 22 August 2020.</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>There were 12 people onboard at the time of the accident. They were 11 pre-booked passengers and 1 skipper.</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AD42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AE42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AF42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AG42" t="inlineStr">
         <is>
           <t>-</t>
         </is>
